--- a/Normalisasi_SalesDB_Fathan.xlsx
+++ b/Normalisasi_SalesDB_Fathan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISK D\MITRA INTEGRASI INFORMATIKA\Bootcamp\Database\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375E075C-E075-4BEE-8359-9CECC28D2567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA84D84-605B-4BB5-AC06-439A0B5AE615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -85,8 +85,74 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="O12" authorId="0" shapeId="0" xr:uid="{EDC6603C-D8C1-4248-8D8C-45D3D38B557A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O13" authorId="0" shapeId="0" xr:uid="{E22976F2-8912-4D31-9ED7-A1757796E7B4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O26" authorId="0" shapeId="0" xr:uid="{0798CEF2-274F-4302-8265-6027B2839795}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O27" authorId="0" shapeId="0" xr:uid="{9E4568E5-A2AC-4920-AB51-9845275C6AB0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="145">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -548,10 +614,28 @@
     <t>Keyboard Mekanik</t>
   </si>
   <si>
-    <t>Kolom A, kolom C, Kolom G, Kolom I</t>
-  </si>
-  <si>
     <t>Saya ubah atomaticity nya, hilangin repeating group, primary key</t>
+  </si>
+  <si>
+    <t>NO FAKTUR = PARTIAL yang menentukan tanggal dan Nama Pelanggan</t>
+  </si>
+  <si>
+    <t>KODE PRODUK = PARTIAL yang menentukan Nama Produk dan Nama Kategori</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>(No Faktur, Kode Pelanggan, Kode Produk, Kode Kategori)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memecah tabel tunggal ke 5 tabel, per tabel dipisahkan kolom kolom ke pada satu PK tertentu, </t>
   </si>
 </sst>
 </file>
@@ -559,9 +643,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,6 +757,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -734,7 +843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -752,7 +861,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -781,7 +890,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -789,8 +898,22 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1592,82 +1715,86 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="25.42578125" customWidth="1"/>
-    <col min="11" max="13" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="13" style="30" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="30" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="30" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="30" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="30" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="30" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="30" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" style="30" customWidth="1"/>
+    <col min="11" max="13" width="12.140625" style="30" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="37" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="33"/>
+      <c r="E6" s="38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="24" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="24" t="s">
@@ -1685,7 +1812,7 @@
       <c r="H11" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="24" t="s">
         <v>30</v>
       </c>
       <c r="J11" s="24" t="s">
@@ -1701,14 +1828,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="28">
         <v>46266</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="25" t="s">
@@ -1726,7 +1853,7 @@
       <c r="H12" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="25" t="s">
         <v>113</v>
       </c>
       <c r="J12" s="25" t="s">
@@ -1742,14 +1869,14 @@
         <v>2150000</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="28">
         <v>46266</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="25" t="s">
@@ -1767,7 +1894,7 @@
       <c r="H13" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="25" t="s">
         <v>114</v>
       </c>
       <c r="J13" s="25" t="s">
@@ -1783,14 +1910,14 @@
         <v>2150000</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="20" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="28">
         <v>46275</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="25" t="s">
@@ -1808,7 +1935,7 @@
       <c r="H14" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="25" t="s">
         <v>121</v>
       </c>
       <c r="J14" s="25" t="s">
@@ -1824,14 +1951,14 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="20" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="28">
         <v>46275</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="25" t="s">
@@ -1849,7 +1976,7 @@
       <c r="H15" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="25" t="s">
         <v>114</v>
       </c>
       <c r="J15" s="25" t="s">
@@ -1865,14 +1992,14 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="28">
         <v>46277</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="25" t="s">
@@ -1890,7 +2017,7 @@
       <c r="H16" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="25" t="s">
         <v>64</v>
       </c>
       <c r="J16" s="25" t="s">
@@ -1906,14 +2033,14 @@
         <v>1050000</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="28">
         <v>46280</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D17" s="25" t="s">
@@ -1931,7 +2058,7 @@
       <c r="H17" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="25" t="s">
         <v>127</v>
       </c>
       <c r="J17" s="25" t="s">
@@ -1947,14 +2074,14 @@
         <v>346000</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="28">
         <v>46280</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="25" t="s">
@@ -1972,7 +2099,7 @@
       <c r="H18" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="25" t="s">
         <v>127</v>
       </c>
       <c r="J18" s="25" t="s">
@@ -1988,14 +2115,14 @@
         <v>346000</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="20" t="s">
         <v>75</v>
       </c>
       <c r="B19" s="28">
         <v>46283</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="25" t="s">
@@ -2013,7 +2140,7 @@
       <c r="H19" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="25" t="s">
         <v>113</v>
       </c>
       <c r="J19" s="25" t="s">
@@ -2029,14 +2156,14 @@
         <v>548000</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="20" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="28">
         <v>46283</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="25" t="s">
@@ -2054,7 +2181,7 @@
       <c r="H20" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="25" t="s">
         <v>127</v>
       </c>
       <c r="J20" s="25" t="s">
@@ -2070,14 +2197,14 @@
         <v>548000</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="20" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="28">
         <v>46283</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="25" t="s">
@@ -2095,7 +2222,7 @@
       <c r="H21" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="25" t="s">
         <v>127</v>
       </c>
       <c r="J21" s="25" t="s">
@@ -2111,14 +2238,14 @@
         <v>548000</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="20" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="28">
         <v>46285</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D22" s="25" t="s">
@@ -2136,7 +2263,7 @@
       <c r="H22" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="25" t="s">
         <v>113</v>
       </c>
       <c r="J22" s="25" t="s">
@@ -2152,14 +2279,14 @@
         <v>4450000</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" s="20" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="28">
         <v>46285</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D23" s="25" t="s">
@@ -2177,7 +2304,7 @@
       <c r="H23" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="30" t="s">
         <v>114</v>
       </c>
       <c r="J23" s="30" t="s">
@@ -2193,8 +2320,8 @@
         <v>4450000</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I24" s="21"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I24" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2203,69 +2330,1194 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:U38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="30" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="30" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="30" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" style="30" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="30" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="30" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="30" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="30" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" style="30" customWidth="1"/>
+    <col min="11" max="12" width="8" style="30" customWidth="1"/>
+    <col min="13" max="15" width="11.42578125" style="30" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="30"/>
+    <col min="17" max="20" width="13.28515625" style="30" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" s="32" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:21" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="36"/>
+      <c r="E7" s="34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="D8" s="36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-    </row>
+    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="U11" s="24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="28">
+        <v>46266</v>
+      </c>
+      <c r="O12" s="29">
+        <v>2150000</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="T12" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U12" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="28">
+        <v>46266</v>
+      </c>
+      <c r="O13" s="29">
+        <v>2150000</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T13" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="U13" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="28">
+        <v>46275</v>
+      </c>
+      <c r="O14" s="29">
+        <v>900000</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R14" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S14" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="T14" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="U14" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="28">
+        <v>46275</v>
+      </c>
+      <c r="O15" s="29">
+        <v>900000</v>
+      </c>
+      <c r="Q15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R15" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S15" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T15" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="U15" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="28">
+        <v>46277</v>
+      </c>
+      <c r="O16" s="29">
+        <v>1050000</v>
+      </c>
+      <c r="Q16" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="R16" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="S16" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="T16" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="U16" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="N17" s="28">
+        <v>46280</v>
+      </c>
+      <c r="O17" s="29">
+        <v>346000</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R17" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="T17" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U17" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J18" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="N18" s="28">
+        <v>46280</v>
+      </c>
+      <c r="O18" s="29">
+        <v>346000</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R18" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T18" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U18" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="N19" s="28">
+        <v>46283</v>
+      </c>
+      <c r="O19" s="29">
+        <v>548000</v>
+      </c>
+      <c r="Q19" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R19" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S19" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="T19" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U19" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" s="28">
+        <v>46283</v>
+      </c>
+      <c r="O20" s="29">
+        <v>548000</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R20" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S20" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="T20" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U20" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="28">
+        <v>46283</v>
+      </c>
+      <c r="O21" s="29">
+        <v>548000</v>
+      </c>
+      <c r="Q21" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R21" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S21" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T21" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U21" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="N22" s="28">
+        <v>46285</v>
+      </c>
+      <c r="O22" s="29">
+        <v>4450000</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R22" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="S22" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="T22" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U22" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" s="40" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="N23" s="28">
+        <v>46285</v>
+      </c>
+      <c r="O23" s="29">
+        <v>4450000</v>
+      </c>
+      <c r="Q23" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R23" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="S23" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="T23" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="U23" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="45" x14ac:dyDescent="0.2">
+      <c r="A25" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="O25" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="S25" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="U25" s="24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="K26" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="N26" s="28">
+        <v>46031</v>
+      </c>
+      <c r="O26" s="29">
+        <v>2150000</v>
+      </c>
+      <c r="Q26" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S26" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="T26" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U26" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="N27" s="28">
+        <v>46304</v>
+      </c>
+      <c r="O27" s="29">
+        <v>900000</v>
+      </c>
+      <c r="Q27" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S27" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T27" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="U27" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="J28" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="K28" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="28">
+        <v>46365</v>
+      </c>
+      <c r="O28" s="29">
+        <v>1050000</v>
+      </c>
+      <c r="Q28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R28" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S28" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="T28" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="U28" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="M29" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="N29" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="O29" s="30">
+        <v>346000</v>
+      </c>
+      <c r="Q29" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R29" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S29" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="T29" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="U29" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I30" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="M30" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="N30" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="O30" s="30">
+        <v>548000</v>
+      </c>
+      <c r="Q30" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="R30" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="S30" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="T30" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="U30" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I31" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="K31" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="M31" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="N31" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="O31" s="30">
+        <v>4450000</v>
+      </c>
+      <c r="Q31" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R31" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="T31" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U31" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R32" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S32" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T32" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U32" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q33" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R33" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S33" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="T33" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U33" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q34" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R34" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S34" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="T34" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U34" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q35" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R35" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S35" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T35" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U35" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q36" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R36" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="S36" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="T36" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U36" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q37" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="R37" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="S37" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="T37" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="U37" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Normalisasi_SalesDB_Fathan.xlsx
+++ b/Normalisasi_SalesDB_Fathan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISK D\MITRA INTEGRASI INFORMATIKA\Bootcamp\Database\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA84D84-605B-4BB5-AC06-439A0B5AE615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF1351F-24DA-43DB-A289-79DCFA9C98FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="ERD" sheetId="6" r:id="rId6"/>
+    <sheet name="QUERY" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -119,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O26" authorId="0" shapeId="0" xr:uid="{0798CEF2-274F-4302-8265-6027B2839795}">
+    <comment ref="O27" authorId="0" shapeId="0" xr:uid="{0798CEF2-274F-4302-8265-6027B2839795}">
       <text>
         <r>
           <rPr>
@@ -133,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O27" authorId="0" shapeId="0" xr:uid="{9E4568E5-A2AC-4920-AB51-9845275C6AB0}">
+    <comment ref="O28" authorId="0" shapeId="0" xr:uid="{9E4568E5-A2AC-4920-AB51-9845275C6AB0}">
       <text>
         <r>
           <rPr>
@@ -152,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="227">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -635,7 +637,5186 @@
     <t>(No Faktur, Kode Pelanggan, Kode Produk, Kode Kategori)</t>
   </si>
   <si>
-    <t xml:space="preserve">Memecah tabel tunggal ke 5 tabel, per tabel dipisahkan kolom kolom ke pada satu PK tertentu, </t>
+    <t xml:space="preserve">Kode Pelanggan </t>
+  </si>
+  <si>
+    <t>Kode Kategori (PK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK)</t>
+  </si>
+  <si>
+    <t>No Faktur (PK)</t>
+  </si>
+  <si>
+    <t>No Faktur (PK,FK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (PK,FK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK,FK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (PK,FK)</t>
+  </si>
+  <si>
+    <t>Memecah tabel tunggal ke 5 tabel, per tabel dipisahkan kolom kolom ke pada satu PK tertentu untuk Menghilangkan ketergantungan parsial (partial dependency)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kode Pelanggan &gt; Nama pelanggan, Email Kota. Nama Kategori &gt; Kode Kategori </t>
+  </si>
+  <si>
+    <t>Tabel pelanggan</t>
+  </si>
+  <si>
+    <t>ORDER DETAIL</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATABASE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <r>
+      <t>USE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>uniqueidentifier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Nvarchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Nvarchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">City </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Nvarchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NONCLUSTERED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INDEX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UX_Customer_Email_Filtered</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Category]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    SubCategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Category]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Nvarchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Product]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Nvarchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Decimal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">CHECK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Category]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    OrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>uniqueidentifier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>datetime2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SYSDATETIME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>uniqueidentifier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [OrderDetail]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    OrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>uniqueidentifier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Product]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Quantity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">CHECK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Quantity </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>decimal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VALUES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'budi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Jakarta'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Siti Aminah'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'siti@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Bandung'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Andi Wijaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'andi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Surabaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--done excecute</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Category]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SubCategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>VALUES</t>
+  </si>
+  <si>
+    <r>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Elektronik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Alat Tulis'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Aksesoris Komputer'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Product]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Monitor 24 inci'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Headset USB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 375000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Buku Catatan A5'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Pulpen Gel (isi 12)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Mouse Wireless'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Keyboard Mekanik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-01'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'D5974860-188D-428A-9C47-098DCDADFB39'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-10'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'47CAC39D-B5C7-4A6F-AB8D-3A7CCB3C084B'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-12'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'020BD935-A2B2-4886-9090-97BCCD88991C'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-15'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'D5974860-188D-428A-9C47-098DCDADFB39'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-18'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'47CAC39D-B5C7-4A6F-AB8D-3A7CCB3C084B'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-20'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'020BD935-A2B2-4886-9090-97BCCD88991C'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [OrderDetail]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Quantity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'011A848F-40A7-4706-993D-D78AA2FBFD05'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'011A848F-40A7-4706-993D-D78AA2FBFD05'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'52FC6DE8-2B90-4FE7-A801-A403EFBF7E53'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'52FC6DE8-2B90-4FE7-A801-A403EFBF7E53'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'A557A6A8-59A4-4EEE-99BF-89C8B62C4E9F'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 375000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'81D1A7E2-111C-4427-BDB6-EF670C3402B5'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'81D1A7E2-111C-4427-BDB6-EF670C3402B5'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'16419C8B-AA75-4352-8369-1D2B454DB8B3'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 375000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'16419C8B-AA75-4352-8369-1D2B454DB8B3'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'16419C8B-AA75-4352-8369-1D2B454DB8B3'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'382CAB3B-0681-4B7F-BFCD-306EF8E3D42E'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'382CAB3B-0681-4B7F-BFCD-306EF8E3D42E'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OrderDetail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -645,7 +5826,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -782,6 +5963,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF008000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -816,7 +6033,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -839,11 +6056,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -898,11 +6124,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -914,6 +6138,69 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -930,6 +6217,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>230844</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>162931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E9F4761-B250-DE52-C681-A7702537E26B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="16080444" cy="7211431"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1719,7 +7055,7 @@
   <cols>
     <col min="1" max="1" width="13" style="30" customWidth="1"/>
     <col min="2" max="2" width="16.140625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="30" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="30" customWidth="1"/>
     <col min="4" max="4" width="12.140625" style="30" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" style="30" customWidth="1"/>
     <col min="6" max="6" width="12.140625" style="30" customWidth="1"/>
@@ -1737,12 +7073,12 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="35" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="35" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1755,8 +7091,8 @@
       <c r="A6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="38" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="36" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1764,13 +7100,13 @@
       <c r="A7" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="36" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1778,7 +7114,7 @@
       <c r="A8" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="34" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2331,133 +7667,161 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U38"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U39"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="30" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="30" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="30" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="30" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="30" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="30" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" style="30" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" style="30" customWidth="1"/>
-    <col min="11" max="12" width="8" style="30" customWidth="1"/>
-    <col min="13" max="15" width="11.42578125" style="30" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="30"/>
-    <col min="17" max="20" width="13.28515625" style="30" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="30"/>
+    <col min="1" max="1" width="13.140625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="38" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="38" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="38" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" style="38" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="38" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="38" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="38" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="38" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" style="38" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="38" customWidth="1"/>
+    <col min="12" max="12" width="8" style="38" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="38" customWidth="1"/>
+    <col min="14" max="14" width="15" style="38" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="38" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="38"/>
+    <col min="17" max="20" width="13.28515625" style="38" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="39" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="41" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="43" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="34" t="s">
-        <v>93</v>
-      </c>
+      <c r="D7" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
     </row>
     <row r="8" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>144</v>
-      </c>
+      <c r="D8" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
     </row>
     <row r="10" spans="1:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="41" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="24" t="s">
+      <c r="N11" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="O11" s="24" t="s">
+      <c r="O11" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="Q11" s="19" t="s">
+      <c r="Q11" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="R11" s="19" t="s">
+      <c r="R11" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="S11" s="19" t="s">
+      <c r="S11" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="T11" s="19" t="s">
+      <c r="T11" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="U11" s="24" t="s">
+      <c r="U11" s="45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>36</v>
       </c>
@@ -2510,7 +7874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>36</v>
       </c>
@@ -2563,7 +7927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>47</v>
       </c>
@@ -2616,7 +7980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>47</v>
       </c>
@@ -2669,7 +8033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>58</v>
       </c>
@@ -2722,7 +8086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>36</v>
       </c>
@@ -2775,7 +8139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>36</v>
       </c>
@@ -2828,7 +8192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>47</v>
       </c>
@@ -2881,7 +8245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>47</v>
       </c>
@@ -2934,7 +8298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>47</v>
       </c>
@@ -2987,7 +8351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>58</v>
       </c>
@@ -3040,7 +8404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="40" customFormat="1" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>58</v>
       </c>
@@ -3053,16 +8417,16 @@
       <c r="D23" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="F23" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="I23" s="39" t="s">
+      <c r="I23" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="J23" s="40" t="s">
+      <c r="J23" s="38" t="s">
         <v>136</v>
       </c>
       <c r="K23" s="25" t="s">
@@ -3083,437 +8447,465 @@
       <c r="R23" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="S23" s="39" t="s">
+      <c r="S23" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="T23" s="39" t="s">
+      <c r="T23" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="U23" s="40">
+      <c r="U23" s="38">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="45" x14ac:dyDescent="0.2">
-      <c r="A25" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="24" t="s">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="F24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="K24" s="53"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="55"/>
+      <c r="Q24" s="52"/>
+      <c r="R24" s="52"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="37"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q25" s="38" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C26" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D26" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="24" t="s">
+      <c r="F26" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I25" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="24" t="s">
+      <c r="I26" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="J26" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="K25" s="24" t="s">
+      <c r="K26" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" s="24" t="s">
+      <c r="M26" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="N26" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="O25" s="24" t="s">
+      <c r="O26" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="Q25" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="R25" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="S25" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="T25" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="U25" s="24" t="s">
+      <c r="Q26" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="R26" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="S26" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="T26" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="U26" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+    <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B27" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C27" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D27" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F27" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="G27" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="I26" s="20" t="s">
+      <c r="I27" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="J27" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="K26" s="25" t="s">
+      <c r="K27" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="M26" s="20" t="s">
+      <c r="M27" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="N26" s="28">
+      <c r="N27" s="28">
         <v>46031</v>
       </c>
-      <c r="O26" s="29">
+      <c r="O27" s="29">
         <v>2150000</v>
       </c>
-      <c r="Q26" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="R26" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="S26" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="T26" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="U26" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J27" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="K27" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="M27" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="N27" s="28">
-        <v>46304</v>
-      </c>
-      <c r="O27" s="29">
-        <v>900000</v>
-      </c>
-      <c r="Q27" s="20" t="s">
+      <c r="Q27" s="46" t="s">
         <v>35</v>
       </c>
       <c r="R27" s="20" t="s">
         <v>36</v>
       </c>
       <c r="S27" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="T27" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U27" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I28" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="J28" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="K28" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="M28" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="N28" s="28">
+        <v>46304</v>
+      </c>
+      <c r="O28" s="29">
+        <v>900000</v>
+      </c>
+      <c r="Q28" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S28" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="T27" s="20" t="s">
+      <c r="T28" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="U27" s="25">
+      <c r="U28" s="25">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
+    <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B29" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C29" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D29" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F29" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G29" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="I28" s="20" t="s">
+      <c r="I29" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="J28" s="25" t="s">
+      <c r="J29" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="K28" s="25" t="s">
+      <c r="K29" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="M28" s="20" t="s">
+      <c r="M29" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="N28" s="28">
+      <c r="N29" s="28">
         <v>46365</v>
       </c>
-      <c r="O28" s="29">
+      <c r="O29" s="29">
         <v>1050000</v>
       </c>
-      <c r="Q28" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="R28" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="S28" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="T28" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="U28" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I29" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="K29" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="M29" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="N29" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="O29" s="30">
-        <v>346000</v>
-      </c>
-      <c r="Q29" s="20" t="s">
+      <c r="Q29" s="46" t="s">
         <v>46</v>
       </c>
       <c r="R29" s="20" t="s">
         <v>47</v>
       </c>
       <c r="S29" s="20" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="T29" s="20" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="U29" s="25">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I30" s="20" t="s">
+    <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I30" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="M30" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="N30" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="O30" s="38">
+        <v>346000</v>
+      </c>
+      <c r="Q30" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="R30" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S30" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="T30" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="U30" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I31" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="J31" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="K30" s="25" t="s">
+      <c r="K31" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="M30" s="30" t="s">
+      <c r="M31" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="N30" s="30" t="s">
+      <c r="N31" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="O30" s="30">
+      <c r="O31" s="38">
         <v>548000</v>
       </c>
-      <c r="Q30" s="20" t="s">
+      <c r="Q31" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="R30" s="20" t="s">
+      <c r="R31" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="S30" s="20" t="s">
+      <c r="S31" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="T30" s="20" t="s">
+      <c r="T31" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="U30" s="25">
+      <c r="U31" s="25">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I31" s="20" t="s">
+    <row r="32" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I32" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="J31" s="25" t="s">
+      <c r="J32" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="K31" s="25" t="s">
+      <c r="K32" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="M31" s="30" t="s">
+      <c r="M32" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="N31" s="30" t="s">
+      <c r="N32" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="O31" s="30">
+      <c r="O32" s="38">
         <v>4450000</v>
       </c>
-      <c r="Q31" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="R31" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="S31" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="T31" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="U31" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q32" s="20" t="s">
+      <c r="Q32" s="46" t="s">
         <v>68</v>
       </c>
       <c r="R32" s="20" t="s">
         <v>36</v>
       </c>
       <c r="S32" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T32" s="20" t="s">
         <v>127</v>
       </c>
       <c r="U32" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q33" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="R33" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S33" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T33" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U33" s="25">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q33" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="R33" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="S33" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="T33" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="U33" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q34" s="20" t="s">
+    <row r="34" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q34" s="46" t="s">
         <v>75</v>
       </c>
       <c r="R34" s="20" t="s">
         <v>47</v>
       </c>
       <c r="S34" s="20" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="T34" s="20" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="U34" s="25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q35" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q35" s="46" t="s">
         <v>75</v>
       </c>
       <c r="R35" s="20" t="s">
         <v>47</v>
       </c>
       <c r="S35" s="20" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="T35" s="20" t="s">
         <v>127</v>
       </c>
       <c r="U35" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q36" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="R36" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S36" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="T36" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="U36" s="25">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q36" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="R36" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="S36" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="T36" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="U36" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q37" s="20" t="s">
+    <row r="37" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q37" s="46" t="s">
         <v>82</v>
       </c>
       <c r="R37" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="S37" s="39" t="s">
+      <c r="S37" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="T37" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="U37" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q38" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="R38" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="S38" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="T37" s="39" t="s">
+      <c r="T38" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="U37" s="40">
+      <c r="U38" s="38">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="17:21" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D8:Q8"/>
+    <mergeCell ref="D7:Q7"/>
+  </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3586,4 +8978,511 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E73330B-AA8F-408B-9963-48061F836E0F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6256E1-202E-46A3-A1E2-ED9ED3CE5132}">
+  <dimension ref="A1:A102"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="89.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="57"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="56" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="58" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="56" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="58" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="58" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="57"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="56" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="57"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="56" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="58" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="58" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="57"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="58" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="58" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="58" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="58" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="57"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="56" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="58" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="58" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="58" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="57"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="56" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="58" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="58" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="57"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="59" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="59" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="57"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="56" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="59" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="59" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="57"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="59" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="59" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="59" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="59" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="59" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="59" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="57"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="56" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="59" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="59" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="59" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="59" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="59" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="57"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="56" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="59" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="59" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="59" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="59" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="59" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="59" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="59" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="59" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="59" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="57"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="56" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Normalisasi_SalesDB_Fathan.xlsx
+++ b/Normalisasi_SalesDB_Fathan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISK D\MITRA INTEGRASI INFORMATIKA\Bootcamp\Database\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF1351F-24DA-43DB-A289-79DCFA9C98FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5856CDA1-3492-4CA1-9E05-B6A76A455E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,20 @@
     <sheet name="ERD" sheetId="6" r:id="rId6"/>
     <sheet name="QUERY" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -154,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="279">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -5817,6 +5830,1942 @@
       </rPr>
       <t>;</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>OUTPUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SubCategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Kotak'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Meja'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Product]   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF008000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>--1850000.00</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1.10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>OUTPUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> deleted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OldPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> NewPrice</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DBCC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CHECKIDENT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'dbo.Category'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> RESEED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Dewi Lestari'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Jakarta'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRODUCT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Product]   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>OUTPUT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> deleted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OldStock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> NewStock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 40</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'011A848F-40A7-4706-993D-D78AA2FBFD05'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>--- The INSERT statement conflicted with the CHECK constraint "CK__OrderDeta__Quant__66603565". The conflict occurred in database "SalesDB", table "dbo.OrderDetail", column 'Quantity'.</t>
+  </si>
+  <si>
+    <t>--- The statement has been terminated.</t>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-24'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 99</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>--- Operand type clash: int is incompatible with uniqueidentifier</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Produk Gagal'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5000.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>product</t>
+    </r>
+  </si>
+  <si>
+    <t>-- Berhasil, karena saya tidak set constraint CHECK Stock &gt;= 0</t>
+  </si>
+  <si>
+    <r>
+      <t>BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TRAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Fathann'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Semarang'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>ROLLBACK</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> customer</t>
+    </r>
+  </si>
+  <si>
+    <t>COMMIT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BudiKWWW'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'budi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'jakartaa'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+  </si>
+  <si>
+    <t>-- Cannot insert duplicate key row in object 'dbo.Customer' with unique index 'UX_Customer_Email_Filtered'. The duplicate key value is (budi@mail.com).</t>
+  </si>
+  <si>
+    <t>-- The statement has been terminated.</t>
+  </si>
+  <si>
+    <t>----- Latihan 1 -------</t>
+  </si>
+  <si>
+    <t>---- Latihan 2 ----</t>
+  </si>
+  <si>
+    <t>---- Latihan 3 ----</t>
+  </si>
+  <si>
+    <t>---- LATIHAN 4 ----</t>
+  </si>
+  <si>
+    <t>-- No 1</t>
+  </si>
+  <si>
+    <t>-- No 2</t>
+  </si>
+  <si>
+    <t>-- No 3</t>
+  </si>
+  <si>
+    <t>-- No 4</t>
+  </si>
+  <si>
+    <t>-- No 5</t>
   </si>
 </sst>
 </file>
@@ -6069,7 +8018,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -6200,6 +8149,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8992,495 +10947,986 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6256E1-202E-46A3-A1E2-ED9ED3CE5132}">
-  <dimension ref="A1:A102"/>
+  <dimension ref="A1:A213"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="89.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="60" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57"/>
-    </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
-        <v>157</v>
-      </c>
+      <c r="A3" s="57"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-    </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="57"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="56" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="58" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="58" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="58" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="58" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="59" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="59" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="56" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57"/>
-    </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
-        <v>165</v>
-      </c>
+      <c r="A15" s="57"/>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-    </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="56" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="58" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="58" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="58" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="59" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="59" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="57"/>
-    </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="56" t="s">
+      <c r="A27" s="57"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="58" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="58" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="58" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="58" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="58" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="59" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="56" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="57"/>
-    </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="57"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="56" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="58" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="58" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="58" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="59" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="59" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="56" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="57"/>
-    </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="57"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="56" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="58" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="58" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="58" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="59" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="59" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="56" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="57"/>
-    </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="56" t="s">
+      <c r="A52" s="57"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="57"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="60" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="56" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="56" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="56" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="59" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="59" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="59" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="59" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="59" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="59" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="56" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="57"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="56" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="57"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="56" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="56" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="59" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="59" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="59" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="59" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="59" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="59" t="s">
         <v>198</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="56" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="57"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="56" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="56" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="59" t="s">
-        <v>200</v>
-      </c>
+      <c r="A68" s="57"/>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="59" t="s">
-        <v>201</v>
+      <c r="A69" s="56" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="59" t="s">
-        <v>202</v>
+      <c r="A70" s="56" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="59" t="s">
-        <v>203</v>
+      <c r="A71" s="56" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="59" t="s">
-        <v>204</v>
+      <c r="A72" s="56" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="59" t="s">
-        <v>205</v>
-      </c>
+      <c r="A73" s="57"/>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="56" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="57"/>
+      <c r="A75" s="56" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="56" t="s">
-        <v>206</v>
+      <c r="A76" s="59" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="56" t="s">
-        <v>189</v>
+      <c r="A77" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="59" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="59" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="59" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="59" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="59" t="s">
-        <v>211</v>
+      <c r="A82" s="56" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="59" t="s">
-        <v>212</v>
-      </c>
+      <c r="A83" s="57"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="56" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="57"/>
+      <c r="A85" s="56" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="56" t="s">
-        <v>213</v>
+      <c r="A86" s="59" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="56" t="s">
-        <v>189</v>
+      <c r="A87" s="59" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="59" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="59" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="59" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="59" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="59" t="s">
-        <v>218</v>
+      <c r="A92" s="56" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="59" t="s">
-        <v>219</v>
-      </c>
+      <c r="A93" s="57"/>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="59" t="s">
-        <v>220</v>
+      <c r="A94" s="56" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="59" t="s">
-        <v>221</v>
+      <c r="A95" s="56" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="59" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="59" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="59" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="59" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="59" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="59" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="59" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="59" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="59" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="59" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="56" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="57"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="56" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="57"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="56" t="s">
         <v>226</v>
       </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="57"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="56" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="57"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="60" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="61" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="56" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="58" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="56" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="57"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="56" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="57"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="56" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="56" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="57"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="56" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="57"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="59" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="57"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="56" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="57"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="61" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="56" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="58" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="56" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="57"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="61" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="56" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="58" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="57"/>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="61" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="56" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="58" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="56" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="57"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="61" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="56" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="58" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="56" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="57"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="60" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="60" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="56" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="56" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="57"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="60" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="60" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="57"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="57"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="60" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="56" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="56" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="57"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="60" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="57"/>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="60" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="56" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="56" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="57"/>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="56" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="60" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="57"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="60" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="56" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="57"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="56" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="57"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="56" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="57"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="56" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="57"/>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="56" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="57"/>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="60" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="56" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="57"/>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="56" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="57"/>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="56" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="57"/>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="56" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="57"/>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="60" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="60" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="60"/>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
